--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.90163</v>
+        <v>16.66495</v>
       </c>
       <c r="D2" t="n">
-        <v>16.43127</v>
+        <v>16.49853</v>
       </c>
       <c r="E2" t="n">
-        <v>16.22623</v>
+        <v>16.64511</v>
       </c>
       <c r="F2" t="n">
-        <v>42.34506</v>
+        <v>42.31276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04929</v>
+        <v>0.0503</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8138</v>
+        <v>1.81574</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73123</v>
+        <v>16.79971</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57134</v>
+        <v>16.39522</v>
       </c>
       <c r="E3" t="n">
-        <v>16.57926</v>
+        <v>16.53304</v>
       </c>
       <c r="F3" t="n">
-        <v>42.34726</v>
+        <v>43.50924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05125</v>
+        <v>0.05023</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83601</v>
+        <v>1.83311</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.88192</v>
+        <v>16.72334</v>
       </c>
       <c r="D4" t="n">
-        <v>16.41437</v>
+        <v>16.52103</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66973</v>
+        <v>16.70823</v>
       </c>
       <c r="F4" t="n">
-        <v>42.75734</v>
+        <v>41.63306</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05143</v>
+        <v>0.05031</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80722</v>
+        <v>1.83428</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.34813</v>
+        <v>16.6712</v>
       </c>
       <c r="D6" t="n">
-        <v>15.78992</v>
+        <v>15.87043</v>
       </c>
       <c r="E6" t="n">
-        <v>16.47261</v>
+        <v>16.27872</v>
       </c>
       <c r="F6" t="n">
-        <v>21.68182</v>
+        <v>21.75797</v>
       </c>
       <c r="G6" t="n">
-        <v>34.00324</v>
+        <v>33.56976</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.37873</v>
+        <v>16.49076</v>
       </c>
       <c r="D7" t="n">
-        <v>15.87634</v>
+        <v>15.95319</v>
       </c>
       <c r="E7" t="n">
-        <v>16.18124</v>
+        <v>16.14964</v>
       </c>
       <c r="F7" t="n">
-        <v>21.93645</v>
+        <v>21.736</v>
       </c>
       <c r="G7" t="n">
-        <v>34.03747</v>
+        <v>33.74681</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68515</v>
+        <v>16.57316</v>
       </c>
       <c r="D8" t="n">
-        <v>16.03798</v>
+        <v>15.9032</v>
       </c>
       <c r="E8" t="n">
-        <v>16.12096</v>
+        <v>16.51503</v>
       </c>
       <c r="F8" t="n">
-        <v>21.21483</v>
+        <v>21.98844</v>
       </c>
       <c r="G8" t="n">
-        <v>34.28263</v>
+        <v>34.11098</v>
       </c>
     </row>
   </sheetData>
